--- a/Documents/Hybrid_RBACplusABAC_DBdesign.xlsx
+++ b/Documents/Hybrid_RBACplusABAC_DBdesign.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitLab\joboffer\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6399035C-1802-47AD-9FD1-A7EF468C078A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C66BE71F-ECB3-4760-87F6-6963792D3766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BEC21941-B947-480A-A7E6-7B63159DE119}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="53">
   <si>
     <t>JobOfferUsers</t>
   </si>
@@ -47,9 +47,6 @@
     <t>Id</t>
   </si>
   <si>
-    <t>AspNetUser_Id</t>
-  </si>
-  <si>
     <t>Name</t>
   </si>
   <si>
@@ -149,9 +146,6 @@
     <t>IsAboveBandOnly</t>
   </si>
   <si>
-    <t>UserCompanyAccess</t>
-  </si>
-  <si>
     <t>UserLegalEntityAccess</t>
   </si>
   <si>
@@ -186,6 +180,24 @@
   </si>
   <si>
     <t>AspNetRoleId</t>
+  </si>
+  <si>
+    <t>AspNetUserId</t>
+  </si>
+  <si>
+    <t>UserRoleCategories</t>
+  </si>
+  <si>
+    <t>CategoryName</t>
+  </si>
+  <si>
+    <t>OrderBy</t>
+  </si>
+  <si>
+    <t>UserDivisionAccess</t>
+  </si>
+  <si>
+    <t>DivisionId</t>
   </si>
 </sst>
 </file>
@@ -566,7 +578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EF47D5C-035D-491F-B6E5-626F15CDCBDA}">
-  <dimension ref="B2:J45"/>
+  <dimension ref="B2:J51"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="16.54296875" bestFit="1" customWidth="1"/>
@@ -581,16 +593,16 @@
         <v>0</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.35">
@@ -612,58 +624,61 @@
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>14</v>
+      </c>
+      <c r="F6" t="s">
+        <v>52</v>
       </c>
       <c r="J6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.35">
@@ -679,68 +694,68 @@
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.35">
       <c r="D13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.35">
       <c r="F14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.35">
       <c r="F15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.35">
       <c r="F16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.35">
       <c r="F17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
       <c r="F18" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
@@ -756,44 +771,44 @@
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D23" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.35">
       <c r="F25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="F26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="F27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B30" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.35">
@@ -803,22 +818,22 @@
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B33" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B37" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="38" spans="2:2" x14ac:dyDescent="0.35">
@@ -828,37 +843,57 @@
     </row>
     <row r="39" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="41" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B42" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B43" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B44" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="45" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B45" t="s">
-        <v>46</v>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B48" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B49" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B50" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B51" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
